--- a/backend/data/medical_master.xlsx
+++ b/backend/data/medical_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/AABA9B7FC384692A/Desktop/LPU/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aaba9b7fc384692a/Desktop/Ai_medical_assitant/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7313785C-7652-4BB8-BD78-FC04FC8A3E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{7313785C-7652-4BB8-BD78-FC04FC8A3E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05705764-9340-45AC-A0C4-59BF17ECD085}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0E185D9D-9B36-489F-B026-23D5259A59E6}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -10425,7 +10423,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10471,6 +10469,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10771,15 +10773,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BD7021-6A2F-41DD-AD14-C9BC8A82637C}">
   <dimension ref="A1:N768"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" customWidth="1"/>
+    <col min="16" max="16" width="17.6640625" customWidth="1"/>
+    <col min="20" max="20" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10823,7 +10827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -10867,7 +10871,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -10911,7 +10915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -10955,7 +10959,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -10999,7 +11003,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -11043,7 +11047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -11087,7 +11091,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -11131,7 +11135,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -11175,7 +11179,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -11219,7 +11223,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -11263,7 +11267,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -11307,7 +11311,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -11351,7 +11355,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -11395,7 +11399,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -11439,7 +11443,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -11483,7 +11487,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -11527,7 +11531,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -11571,7 +11575,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>101</v>
       </c>
@@ -11615,7 +11619,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -11659,7 +11663,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>111</v>
       </c>
@@ -11703,7 +11707,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -11747,7 +11751,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -11791,7 +11795,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -11835,7 +11839,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>129</v>
       </c>
@@ -11879,7 +11883,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -11923,7 +11927,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>139</v>
       </c>
@@ -11967,7 +11971,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>144</v>
       </c>
@@ -12011,7 +12015,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>149</v>
       </c>
@@ -12055,7 +12059,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>154</v>
       </c>
@@ -12099,7 +12103,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>159</v>
       </c>
@@ -12143,7 +12147,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>164</v>
       </c>
@@ -12187,7 +12191,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>168</v>
       </c>
@@ -12231,7 +12235,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>173</v>
       </c>
@@ -12275,7 +12279,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>178</v>
       </c>
@@ -12319,7 +12323,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>184</v>
       </c>
@@ -12363,7 +12367,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>188</v>
       </c>
@@ -12407,7 +12411,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>192</v>
       </c>
@@ -12451,7 +12455,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>195</v>
       </c>
@@ -12495,7 +12499,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>198</v>
       </c>
@@ -12539,7 +12543,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>201</v>
       </c>
@@ -12583,7 +12587,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>204</v>
       </c>
@@ -12627,7 +12631,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>209</v>
       </c>
@@ -12671,7 +12675,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>214</v>
       </c>
@@ -12715,7 +12719,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>221</v>
       </c>
@@ -12759,7 +12763,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>226</v>
       </c>
@@ -12803,7 +12807,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>231</v>
       </c>
@@ -12847,7 +12851,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>236</v>
       </c>
@@ -12891,7 +12895,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>241</v>
       </c>
@@ -12935,7 +12939,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>247</v>
       </c>
@@ -12979,7 +12983,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>253</v>
       </c>
@@ -13023,7 +13027,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>257</v>
       </c>
@@ -13067,7 +13071,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>261</v>
       </c>
@@ -13111,7 +13115,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>266</v>
       </c>
@@ -13155,7 +13159,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>270</v>
       </c>
@@ -13199,7 +13203,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>274</v>
       </c>
@@ -13243,7 +13247,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>279</v>
       </c>
@@ -13287,7 +13291,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>285</v>
       </c>
@@ -13331,7 +13335,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>290</v>
       </c>
@@ -13375,7 +13379,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>295</v>
       </c>
@@ -13419,7 +13423,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>301</v>
       </c>
@@ -13463,7 +13467,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>307</v>
       </c>
@@ -13507,7 +13511,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>312</v>
       </c>
@@ -13551,7 +13555,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>318</v>
       </c>
@@ -13595,7 +13599,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>323</v>
       </c>
@@ -13639,7 +13643,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>328</v>
       </c>
@@ -13683,7 +13687,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>333</v>
       </c>
@@ -13727,7 +13731,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>338</v>
       </c>
@@ -13771,7 +13775,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>343</v>
       </c>
@@ -13815,7 +13819,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>348</v>
       </c>
@@ -13859,7 +13863,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>354</v>
       </c>
@@ -13903,7 +13907,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>359</v>
       </c>
@@ -13947,7 +13951,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>364</v>
       </c>
@@ -13991,7 +13995,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>368</v>
       </c>
@@ -14035,7 +14039,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>374</v>
       </c>
@@ -14079,7 +14083,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>379</v>
       </c>
@@ -14123,7 +14127,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>384</v>
       </c>
@@ -14167,7 +14171,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>389</v>
       </c>
@@ -14211,7 +14215,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>394</v>
       </c>
@@ -14255,7 +14259,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>399</v>
       </c>
@@ -14299,7 +14303,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>405</v>
       </c>
@@ -14343,7 +14347,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>410</v>
       </c>
@@ -14387,7 +14391,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>414</v>
       </c>
@@ -14431,7 +14435,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>418</v>
       </c>
@@ -14475,7 +14479,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>423</v>
       </c>
@@ -14519,7 +14523,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>428</v>
       </c>
@@ -14563,7 +14567,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>433</v>
       </c>
@@ -14607,7 +14611,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>438</v>
       </c>
@@ -14651,7 +14655,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>443</v>
       </c>
@@ -14695,7 +14699,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>448</v>
       </c>
@@ -14739,7 +14743,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>453</v>
       </c>
@@ -14783,7 +14787,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>457</v>
       </c>
@@ -14827,7 +14831,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>462</v>
       </c>
@@ -14871,7 +14875,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>467</v>
       </c>
@@ -14915,7 +14919,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>471</v>
       </c>
@@ -14959,7 +14963,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>475</v>
       </c>
@@ -15003,7 +15007,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>478</v>
       </c>
@@ -15047,7 +15051,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>484</v>
       </c>
@@ -15091,7 +15095,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>490</v>
       </c>
@@ -15135,7 +15139,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>496</v>
       </c>
@@ -15179,7 +15183,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>501</v>
       </c>
@@ -15223,7 +15227,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>506</v>
       </c>
@@ -15267,7 +15271,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>511</v>
       </c>
@@ -15311,7 +15315,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>516</v>
       </c>
@@ -15355,7 +15359,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>522</v>
       </c>
@@ -15399,7 +15403,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>526</v>
       </c>
@@ -15443,7 +15447,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>531</v>
       </c>
@@ -15487,7 +15491,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>536</v>
       </c>
@@ -15531,7 +15535,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>541</v>
       </c>
@@ -15575,7 +15579,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>546</v>
       </c>
@@ -15619,7 +15623,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>551</v>
       </c>
@@ -15663,7 +15667,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>556</v>
       </c>
@@ -15707,7 +15711,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>560</v>
       </c>
@@ -15751,7 +15755,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>565</v>
       </c>
@@ -15795,7 +15799,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>570</v>
       </c>
@@ -15839,7 +15843,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>575</v>
       </c>
@@ -15883,7 +15887,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>581</v>
       </c>
@@ -15927,7 +15931,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>586</v>
       </c>
@@ -15971,7 +15975,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>591</v>
       </c>
@@ -16015,7 +16019,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>596</v>
       </c>
@@ -16059,7 +16063,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>601</v>
       </c>
@@ -16103,7 +16107,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>606</v>
       </c>
@@ -16147,7 +16151,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>611</v>
       </c>
@@ -16191,7 +16195,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>616</v>
       </c>
@@ -16235,7 +16239,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>622</v>
       </c>
@@ -16279,7 +16283,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>627</v>
       </c>
@@ -16323,7 +16327,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>632</v>
       </c>
@@ -16367,7 +16371,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>636</v>
       </c>
@@ -16411,7 +16415,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>641</v>
       </c>
@@ -16455,7 +16459,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>646</v>
       </c>
@@ -16499,7 +16503,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>651</v>
       </c>
@@ -16543,7 +16547,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>656</v>
       </c>
@@ -16587,7 +16591,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>661</v>
       </c>
@@ -16631,7 +16635,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>667</v>
       </c>
@@ -16675,7 +16679,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>673</v>
       </c>
@@ -16719,7 +16723,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>678</v>
       </c>
@@ -16763,7 +16767,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>683</v>
       </c>
@@ -16807,7 +16811,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>688</v>
       </c>
@@ -16851,7 +16855,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>693</v>
       </c>
@@ -16895,7 +16899,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>698</v>
       </c>
@@ -16939,7 +16943,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>704</v>
       </c>
@@ -16983,7 +16987,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>709</v>
       </c>
@@ -17027,7 +17031,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>714</v>
       </c>
@@ -17071,7 +17075,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>719</v>
       </c>
@@ -17115,7 +17119,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>724</v>
       </c>
@@ -17159,7 +17163,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>729</v>
       </c>
@@ -17203,7 +17207,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>734</v>
       </c>
@@ -17247,7 +17251,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>736</v>
       </c>
@@ -17291,7 +17295,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>741</v>
       </c>
@@ -17335,7 +17339,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>746</v>
       </c>
@@ -17379,7 +17383,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>751</v>
       </c>
@@ -17423,7 +17427,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>756</v>
       </c>
@@ -17467,7 +17471,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>761</v>
       </c>
@@ -17511,7 +17515,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>766</v>
       </c>
@@ -17555,7 +17559,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>770</v>
       </c>
@@ -17599,7 +17603,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>774</v>
       </c>
@@ -17643,7 +17647,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>779</v>
       </c>
@@ -17687,7 +17691,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>784</v>
       </c>
@@ -17731,7 +17735,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>789</v>
       </c>
@@ -17775,7 +17779,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>793</v>
       </c>
@@ -17819,7 +17823,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>797</v>
       </c>
@@ -17863,7 +17867,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>801</v>
       </c>
@@ -17907,7 +17911,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>805</v>
       </c>
@@ -17951,7 +17955,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>810</v>
       </c>
@@ -17995,7 +17999,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>816</v>
       </c>
@@ -18039,7 +18043,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>822</v>
       </c>
@@ -18083,7 +18087,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>828</v>
       </c>
@@ -18127,7 +18131,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>834</v>
       </c>
@@ -18171,7 +18175,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>839</v>
       </c>
@@ -18215,7 +18219,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>843</v>
       </c>
@@ -18259,7 +18263,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>848</v>
       </c>
@@ -18303,7 +18307,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>853</v>
       </c>
@@ -18347,7 +18351,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>857</v>
       </c>
@@ -18391,7 +18395,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>863</v>
       </c>
@@ -18435,7 +18439,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>867</v>
       </c>
@@ -18479,7 +18483,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>871</v>
       </c>
@@ -18523,7 +18527,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>876</v>
       </c>
@@ -18567,7 +18571,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>879</v>
       </c>
@@ -18611,7 +18615,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>882</v>
       </c>
@@ -18655,7 +18659,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>886</v>
       </c>
@@ -18699,7 +18703,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>891</v>
       </c>
@@ -18743,7 +18747,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>896</v>
       </c>
@@ -18787,7 +18791,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>901</v>
       </c>
@@ -18831,7 +18835,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>906</v>
       </c>
@@ -18875,7 +18879,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>910</v>
       </c>
@@ -18919,7 +18923,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>914</v>
       </c>
@@ -18963,7 +18967,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>919</v>
       </c>
@@ -19007,7 +19011,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>924</v>
       </c>
@@ -19051,7 +19055,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>930</v>
       </c>
@@ -19095,7 +19099,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>936</v>
       </c>
@@ -19139,7 +19143,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>941</v>
       </c>
@@ -19183,7 +19187,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>947</v>
       </c>
@@ -19227,7 +19231,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="193" spans="1:14">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>952</v>
       </c>
@@ -19271,7 +19275,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="194" spans="1:14">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>958</v>
       </c>
@@ -19315,7 +19319,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="195" spans="1:14">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>963</v>
       </c>
@@ -19359,7 +19363,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="196" spans="1:14">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>967</v>
       </c>
@@ -19403,7 +19407,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>971</v>
       </c>
@@ -19447,7 +19451,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="198" spans="1:14">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>974</v>
       </c>
@@ -19491,7 +19495,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="199" spans="1:14">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>978</v>
       </c>
@@ -19535,7 +19539,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="200" spans="1:14">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>983</v>
       </c>
@@ -19579,7 +19583,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="201" spans="1:14">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>984</v>
       </c>
@@ -19623,7 +19627,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>985</v>
       </c>
@@ -19667,7 +19671,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="203" spans="1:14">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>988</v>
       </c>
@@ -19711,7 +19715,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="204" spans="1:14">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>993</v>
       </c>
@@ -19755,7 +19759,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="205" spans="1:14">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>997</v>
       </c>
@@ -19799,7 +19803,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="206" spans="1:14">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1000</v>
       </c>
@@ -19843,7 +19847,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1004</v>
       </c>
@@ -19887,7 +19891,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="208" spans="1:14">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1006</v>
       </c>
@@ -19931,7 +19935,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>1008</v>
       </c>
@@ -19975,7 +19979,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>1010</v>
       </c>
@@ -20019,7 +20023,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1016</v>
       </c>
@@ -20063,7 +20067,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1021</v>
       </c>
@@ -20107,7 +20111,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>1025</v>
       </c>
@@ -20151,7 +20155,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>1028</v>
       </c>
@@ -20195,7 +20199,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1031</v>
       </c>
@@ -20239,7 +20243,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>1036</v>
       </c>
@@ -20283,7 +20287,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1041</v>
       </c>
@@ -20327,7 +20331,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>1046</v>
       </c>
@@ -20371,7 +20375,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>1052</v>
       </c>
@@ -20415,7 +20419,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1057</v>
       </c>
@@ -20459,7 +20463,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>1063</v>
       </c>
@@ -20503,7 +20507,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>1068</v>
       </c>
@@ -20547,7 +20551,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1073</v>
       </c>
@@ -20591,7 +20595,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>1078</v>
       </c>
@@ -20635,7 +20639,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="225" spans="1:14">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1084</v>
       </c>
@@ -20679,7 +20683,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="226" spans="1:14">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1089</v>
       </c>
@@ -20723,7 +20727,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1094</v>
       </c>
@@ -20767,7 +20771,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="228" spans="1:14">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1096</v>
       </c>
@@ -20811,7 +20815,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="229" spans="1:14">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1097</v>
       </c>
@@ -20855,7 +20859,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="230" spans="1:14">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1098</v>
       </c>
@@ -20899,7 +20903,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="231" spans="1:14">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1101</v>
       </c>
@@ -20943,7 +20947,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1104</v>
       </c>
@@ -20987,7 +20991,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1106</v>
       </c>
@@ -21031,7 +21035,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1111</v>
       </c>
@@ -21075,7 +21079,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1116</v>
       </c>
@@ -21119,7 +21123,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1119</v>
       </c>
@@ -21163,7 +21167,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1124</v>
       </c>
@@ -21207,7 +21211,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1128</v>
       </c>
@@ -21251,7 +21255,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1132</v>
       </c>
@@ -21295,7 +21299,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1137</v>
       </c>
@@ -21339,7 +21343,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1142</v>
       </c>
@@ -21383,7 +21387,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1147</v>
       </c>
@@ -21427,7 +21431,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1152</v>
       </c>
@@ -21471,7 +21475,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1157</v>
       </c>
@@ -21515,7 +21519,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1162</v>
       </c>
@@ -21559,7 +21563,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1167</v>
       </c>
@@ -21603,7 +21607,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1172</v>
       </c>
@@ -21647,7 +21651,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1177</v>
       </c>
@@ -21691,7 +21695,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1180</v>
       </c>
@@ -21735,7 +21739,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1185</v>
       </c>
@@ -21779,7 +21783,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1190</v>
       </c>
@@ -21823,7 +21827,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1195</v>
       </c>
@@ -21867,7 +21871,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1198</v>
       </c>
@@ -21911,7 +21915,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1202</v>
       </c>
@@ -21955,7 +21959,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1205</v>
       </c>
@@ -21999,7 +22003,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1209</v>
       </c>
@@ -22043,7 +22047,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1213</v>
       </c>
@@ -22087,7 +22091,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1218</v>
       </c>
@@ -22131,7 +22135,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1220</v>
       </c>
@@ -22175,7 +22179,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1223</v>
       </c>
@@ -22219,7 +22223,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1226</v>
       </c>
@@ -22263,7 +22267,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1231</v>
       </c>
@@ -22307,7 +22311,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1236</v>
       </c>
@@ -22351,7 +22355,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1242</v>
       </c>
@@ -22395,7 +22399,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1248</v>
       </c>
@@ -22439,7 +22443,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1252</v>
       </c>
@@ -22483,7 +22487,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1257</v>
       </c>
@@ -22527,7 +22531,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1262</v>
       </c>
@@ -22571,7 +22575,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1266</v>
       </c>
@@ -22615,7 +22619,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1271</v>
       </c>
@@ -22659,7 +22663,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1275</v>
       </c>
@@ -22703,7 +22707,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1278</v>
       </c>
@@ -22747,7 +22751,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1283</v>
       </c>
@@ -22791,7 +22795,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1287</v>
       </c>
@@ -22835,7 +22839,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1291</v>
       </c>
@@ -22879,7 +22883,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1296</v>
       </c>
@@ -22923,7 +22927,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1298</v>
       </c>
@@ -22967,7 +22971,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1302</v>
       </c>
@@ -23011,7 +23015,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1306</v>
       </c>
@@ -23055,7 +23059,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1312</v>
       </c>
@@ -23099,7 +23103,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1316</v>
       </c>
@@ -23143,7 +23147,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1321</v>
       </c>
@@ -23187,7 +23191,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1326</v>
       </c>
@@ -23231,7 +23235,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1330</v>
       </c>
@@ -23275,7 +23279,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1336</v>
       </c>
@@ -23319,7 +23323,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1341</v>
       </c>
@@ -23363,7 +23367,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1344</v>
       </c>
@@ -23407,7 +23411,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1349</v>
       </c>
@@ -23451,7 +23455,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="289" spans="1:14">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1355</v>
       </c>
@@ -23495,7 +23499,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="290" spans="1:14">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1361</v>
       </c>
@@ -23539,7 +23543,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="291" spans="1:14">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1366</v>
       </c>
@@ -23583,7 +23587,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="292" spans="1:14">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1371</v>
       </c>
@@ -23627,7 +23631,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="293" spans="1:14">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>1377</v>
       </c>
@@ -23671,7 +23675,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="294" spans="1:14">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1382</v>
       </c>
@@ -23715,7 +23719,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="295" spans="1:14">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1386</v>
       </c>
@@ -23759,7 +23763,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="296" spans="1:14">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1388</v>
       </c>
@@ -23803,7 +23807,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="297" spans="1:14">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1393</v>
       </c>
@@ -23847,7 +23851,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="298" spans="1:14">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1398</v>
       </c>
@@ -23891,7 +23895,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="299" spans="1:14">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1403</v>
       </c>
@@ -23935,7 +23939,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="300" spans="1:14">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1405</v>
       </c>
@@ -23979,7 +23983,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="301" spans="1:14">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1411</v>
       </c>
@@ -24023,7 +24027,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="302" spans="1:14">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1417</v>
       </c>
@@ -24067,7 +24071,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="303" spans="1:14">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1422</v>
       </c>
@@ -24111,7 +24115,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="304" spans="1:14">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1426</v>
       </c>
@@ -24155,7 +24159,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="305" spans="1:14">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1431</v>
       </c>
@@ -24199,7 +24203,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="306" spans="1:14">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1436</v>
       </c>
@@ -24243,7 +24247,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="307" spans="1:14">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1440</v>
       </c>
@@ -24287,7 +24291,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="308" spans="1:14">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1443</v>
       </c>
@@ -24331,7 +24335,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="309" spans="1:14">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1448</v>
       </c>
@@ -24375,7 +24379,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="310" spans="1:14">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1453</v>
       </c>
@@ -24419,7 +24423,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="311" spans="1:14">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1458</v>
       </c>
@@ -24463,7 +24467,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="312" spans="1:14">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1463</v>
       </c>
@@ -24507,7 +24511,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="313" spans="1:14">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1468</v>
       </c>
@@ -24551,7 +24555,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="314" spans="1:14">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1473</v>
       </c>
@@ -24595,7 +24599,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="315" spans="1:14">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1478</v>
       </c>
@@ -24639,7 +24643,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="316" spans="1:14">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1483</v>
       </c>
@@ -24683,7 +24687,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="317" spans="1:14">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1488</v>
       </c>
@@ -24727,7 +24731,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="318" spans="1:14">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1493</v>
       </c>
@@ -24771,7 +24775,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="319" spans="1:14">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1497</v>
       </c>
@@ -24815,7 +24819,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="320" spans="1:14">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1502</v>
       </c>
@@ -24859,7 +24863,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="321" spans="1:14">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>1507</v>
       </c>
@@ -24903,7 +24907,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="322" spans="1:14">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1512</v>
       </c>
@@ -24947,7 +24951,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1516</v>
       </c>
@@ -24991,7 +24995,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>1521</v>
       </c>
@@ -25035,7 +25039,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1527</v>
       </c>
@@ -25079,7 +25083,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1532</v>
       </c>
@@ -25123,7 +25127,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1537</v>
       </c>
@@ -25167,7 +25171,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1542</v>
       </c>
@@ -25211,7 +25215,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1547</v>
       </c>
@@ -25255,7 +25259,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1552</v>
       </c>
@@ -25299,7 +25303,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1557</v>
       </c>
@@ -25343,7 +25347,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1562</v>
       </c>
@@ -25387,7 +25391,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1567</v>
       </c>
@@ -25431,7 +25435,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1572</v>
       </c>
@@ -25475,7 +25479,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1575</v>
       </c>
@@ -25519,7 +25523,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1580</v>
       </c>
@@ -25563,7 +25567,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="337" spans="1:14">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1584</v>
       </c>
@@ -25607,7 +25611,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="338" spans="1:14">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1587</v>
       </c>
@@ -25651,7 +25655,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="339" spans="1:14">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1590</v>
       </c>
@@ -25695,7 +25699,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="340" spans="1:14">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1592</v>
       </c>
@@ -25739,7 +25743,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="341" spans="1:14">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1595</v>
       </c>
@@ -25783,7 +25787,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="342" spans="1:14">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1599</v>
       </c>
@@ -25827,7 +25831,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="343" spans="1:14">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1602</v>
       </c>
@@ -25871,7 +25875,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="344" spans="1:14">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1605</v>
       </c>
@@ -25915,7 +25919,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="345" spans="1:14">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1607</v>
       </c>
@@ -25959,7 +25963,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="346" spans="1:14">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1611</v>
       </c>
@@ -26003,7 +26007,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="347" spans="1:14">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1615</v>
       </c>
@@ -26047,7 +26051,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="348" spans="1:14">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1619</v>
       </c>
@@ -26091,7 +26095,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="349" spans="1:14">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1622</v>
       </c>
@@ -26135,7 +26139,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1625</v>
       </c>
@@ -26179,7 +26183,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1628</v>
       </c>
@@ -26223,7 +26227,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1632</v>
       </c>
@@ -26267,7 +26271,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1636</v>
       </c>
@@ -26311,7 +26315,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1642</v>
       </c>
@@ -26355,7 +26359,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1645</v>
       </c>
@@ -26399,7 +26403,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1650</v>
       </c>
@@ -26443,7 +26447,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1655</v>
       </c>
@@ -26487,7 +26491,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1660</v>
       </c>
@@ -26531,7 +26535,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1666</v>
       </c>
@@ -26575,7 +26579,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1671</v>
       </c>
@@ -26619,7 +26623,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1673</v>
       </c>
@@ -26663,7 +26667,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1675</v>
       </c>
@@ -26707,7 +26711,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1678</v>
       </c>
@@ -26751,7 +26755,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="364" spans="1:14">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1681</v>
       </c>
@@ -26795,7 +26799,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="365" spans="1:14">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1685</v>
       </c>
@@ -26839,7 +26843,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="366" spans="1:14">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1689</v>
       </c>
@@ -26883,7 +26887,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="367" spans="1:14">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1694</v>
       </c>
@@ -26927,7 +26931,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="368" spans="1:14">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1699</v>
       </c>
@@ -26971,7 +26975,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="369" spans="1:14">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1704</v>
       </c>
@@ -27015,7 +27019,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="370" spans="1:14">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1709</v>
       </c>
@@ -27059,7 +27063,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>1712</v>
       </c>
@@ -27103,7 +27107,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1715</v>
       </c>
@@ -27147,7 +27151,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>1719</v>
       </c>
@@ -27191,7 +27195,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>1723</v>
       </c>
@@ -27235,7 +27239,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="375" spans="1:14">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>1727</v>
       </c>
@@ -27279,7 +27283,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="376" spans="1:14">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>1732</v>
       </c>
@@ -27323,7 +27327,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="377" spans="1:14">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>1736</v>
       </c>
@@ -27367,7 +27371,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="378" spans="1:14">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>1741</v>
       </c>
@@ -27411,7 +27415,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="379" spans="1:14">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>1746</v>
       </c>
@@ -27455,7 +27459,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="380" spans="1:14">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>1749</v>
       </c>
@@ -27499,7 +27503,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>1751</v>
       </c>
@@ -27543,7 +27547,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>1756</v>
       </c>
@@ -27587,7 +27591,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>1760</v>
       </c>
@@ -27631,7 +27635,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>1764</v>
       </c>
@@ -27675,7 +27679,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1769</v>
       </c>
@@ -27719,7 +27723,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>1774</v>
       </c>
@@ -27763,7 +27767,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>1779</v>
       </c>
@@ -27807,7 +27811,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>1783</v>
       </c>
@@ -27851,7 +27855,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>1788</v>
       </c>
@@ -27895,7 +27899,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>1792</v>
       </c>
@@ -27939,7 +27943,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>1796</v>
       </c>
@@ -27983,7 +27987,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>1800</v>
       </c>
@@ -28027,7 +28031,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="393" spans="1:14">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1804</v>
       </c>
@@ -28071,7 +28075,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="394" spans="1:14">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>1809</v>
       </c>
@@ -28115,7 +28119,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="395" spans="1:14">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>1815</v>
       </c>
@@ -28159,7 +28163,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="396" spans="1:14">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1818</v>
       </c>
@@ -28203,7 +28207,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="397" spans="1:14">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>1821</v>
       </c>
@@ -28247,7 +28251,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="398" spans="1:14">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1825</v>
       </c>
@@ -28291,7 +28295,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1827</v>
       </c>
@@ -28335,7 +28339,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1832</v>
       </c>
@@ -28379,7 +28383,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="401" spans="1:14">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>1837</v>
       </c>
@@ -28423,7 +28427,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="402" spans="1:14">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1842</v>
       </c>
@@ -28467,7 +28471,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="403" spans="1:14">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>1847</v>
       </c>
@@ -28511,7 +28515,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="404" spans="1:14">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>1852</v>
       </c>
@@ -28555,7 +28559,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="405" spans="1:14">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>1854</v>
       </c>
@@ -28599,7 +28603,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="406" spans="1:14">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>1856</v>
       </c>
@@ -28643,7 +28647,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="407" spans="1:14">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1858</v>
       </c>
@@ -28687,7 +28691,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="408" spans="1:14">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1860</v>
       </c>
@@ -28731,7 +28735,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="409" spans="1:14">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1865</v>
       </c>
@@ -28775,7 +28779,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="410" spans="1:14">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1869</v>
       </c>
@@ -28819,7 +28823,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="411" spans="1:14">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>1873</v>
       </c>
@@ -28863,7 +28867,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="412" spans="1:14">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1878</v>
       </c>
@@ -28907,7 +28911,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="413" spans="1:14">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1882</v>
       </c>
@@ -28951,7 +28955,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="414" spans="1:14">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1886</v>
       </c>
@@ -28995,7 +28999,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="415" spans="1:14">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1890</v>
       </c>
@@ -29039,7 +29043,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="416" spans="1:14">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1894</v>
       </c>
@@ -29083,7 +29087,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="417" spans="1:14">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1898</v>
       </c>
@@ -29127,7 +29131,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="418" spans="1:14">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1902</v>
       </c>
@@ -29171,7 +29175,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="419" spans="1:14">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1906</v>
       </c>
@@ -29215,7 +29219,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="420" spans="1:14">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1910</v>
       </c>
@@ -29259,7 +29263,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="421" spans="1:14">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1915</v>
       </c>
@@ -29303,7 +29307,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="422" spans="1:14">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1920</v>
       </c>
@@ -29347,7 +29351,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="423" spans="1:14">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1925</v>
       </c>
@@ -29391,7 +29395,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="424" spans="1:14">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1929</v>
       </c>
@@ -29435,7 +29439,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="425" spans="1:14">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1934</v>
       </c>
@@ -29479,7 +29483,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="426" spans="1:14">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1939</v>
       </c>
@@ -29523,7 +29527,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="427" spans="1:14">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1944</v>
       </c>
@@ -29567,7 +29571,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="428" spans="1:14">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1949</v>
       </c>
@@ -29611,7 +29615,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="429" spans="1:14">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1954</v>
       </c>
@@ -29655,7 +29659,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="430" spans="1:14">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1961</v>
       </c>
@@ -29699,7 +29703,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="431" spans="1:14">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1966</v>
       </c>
@@ -29743,7 +29747,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="432" spans="1:14">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1972</v>
       </c>
@@ -29787,7 +29791,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="433" spans="1:14">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1977</v>
       </c>
@@ -29831,7 +29835,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="434" spans="1:14">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1982</v>
       </c>
@@ -29875,7 +29879,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="435" spans="1:14">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1986</v>
       </c>
@@ -29919,7 +29923,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="436" spans="1:14">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1991</v>
       </c>
@@ -29963,7 +29967,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="437" spans="1:14">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1996</v>
       </c>
@@ -30007,7 +30011,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="438" spans="1:14">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>2001</v>
       </c>
@@ -30051,7 +30055,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="439" spans="1:14">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>2006</v>
       </c>
@@ -30095,7 +30099,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="440" spans="1:14">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>2010</v>
       </c>
@@ -30139,7 +30143,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="441" spans="1:14">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>2015</v>
       </c>
@@ -30183,7 +30187,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="442" spans="1:14">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>2020</v>
       </c>
@@ -30227,7 +30231,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="443" spans="1:14">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>2025</v>
       </c>
@@ -30271,7 +30275,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="444" spans="1:14">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>2030</v>
       </c>
@@ -30315,7 +30319,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="445" spans="1:14">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>2034</v>
       </c>
@@ -30359,7 +30363,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="446" spans="1:14">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>2039</v>
       </c>
@@ -30403,7 +30407,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="447" spans="1:14">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>2041</v>
       </c>
@@ -30447,7 +30451,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="448" spans="1:14">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>2046</v>
       </c>
@@ -30491,7 +30495,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="449" spans="1:14">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>2051</v>
       </c>
@@ -30535,7 +30539,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="450" spans="1:14">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>2056</v>
       </c>
@@ -30579,7 +30583,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="451" spans="1:14">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>2061</v>
       </c>
@@ -30623,7 +30627,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="452" spans="1:14">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>2066</v>
       </c>
@@ -30667,7 +30671,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="453" spans="1:14">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>2071</v>
       </c>
@@ -30711,7 +30715,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="454" spans="1:14">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>2076</v>
       </c>
@@ -30755,7 +30759,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="455" spans="1:14">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>2080</v>
       </c>
@@ -30799,7 +30803,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="456" spans="1:14">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>2085</v>
       </c>
@@ -30843,7 +30847,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="457" spans="1:14">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>2090</v>
       </c>
@@ -30887,7 +30891,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="458" spans="1:14">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>2094</v>
       </c>
@@ -30931,7 +30935,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="459" spans="1:14">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>2099</v>
       </c>
@@ -30975,7 +30979,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="460" spans="1:14">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>2103</v>
       </c>
@@ -31019,7 +31023,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="461" spans="1:14">
+    <row r="461" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>2108</v>
       </c>
@@ -31063,7 +31067,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="462" spans="1:14">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>2113</v>
       </c>
@@ -31107,7 +31111,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="463" spans="1:14">
+    <row r="463" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>2118</v>
       </c>
@@ -31151,7 +31155,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="464" spans="1:14">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>2123</v>
       </c>
@@ -31195,7 +31199,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="465" spans="1:14">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>2128</v>
       </c>
@@ -31239,7 +31243,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="466" spans="1:14">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>2133</v>
       </c>
@@ -31283,7 +31287,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="467" spans="1:14">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>2138</v>
       </c>
@@ -31327,7 +31331,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="468" spans="1:14">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>2141</v>
       </c>
@@ -31371,7 +31375,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="469" spans="1:14">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>2143</v>
       </c>
@@ -31415,7 +31419,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="470" spans="1:14">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>2148</v>
       </c>
@@ -31459,7 +31463,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="471" spans="1:14">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>2153</v>
       </c>
@@ -31503,7 +31507,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="472" spans="1:14">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>2158</v>
       </c>
@@ -31547,7 +31551,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="473" spans="1:14">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>2163</v>
       </c>
@@ -31591,7 +31595,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="474" spans="1:14">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>2167</v>
       </c>
@@ -31635,7 +31639,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="475" spans="1:14">
+    <row r="475" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>2169</v>
       </c>
@@ -31679,7 +31683,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="476" spans="1:14">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>2174</v>
       </c>
@@ -31723,7 +31727,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="477" spans="1:14">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>2176</v>
       </c>
@@ -31767,7 +31771,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="478" spans="1:14">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>2178</v>
       </c>
@@ -31811,7 +31815,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="479" spans="1:14">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>2182</v>
       </c>
@@ -31855,7 +31859,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="480" spans="1:14">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>2187</v>
       </c>
@@ -31899,7 +31903,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="481" spans="1:14">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>2191</v>
       </c>
@@ -31943,7 +31947,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="482" spans="1:14">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>2195</v>
       </c>
@@ -31987,7 +31991,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="483" spans="1:14">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>2201</v>
       </c>
@@ -32031,7 +32035,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="484" spans="1:14">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>2206</v>
       </c>
@@ -32075,7 +32079,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="485" spans="1:14">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>2211</v>
       </c>
@@ -32119,7 +32123,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="486" spans="1:14">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>2216</v>
       </c>
@@ -32163,7 +32167,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="487" spans="1:14">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>2221</v>
       </c>
@@ -32207,7 +32211,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="488" spans="1:14">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>2225</v>
       </c>
@@ -32251,7 +32255,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="489" spans="1:14">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>2230</v>
       </c>
@@ -32295,7 +32299,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="490" spans="1:14">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>2234</v>
       </c>
@@ -32339,7 +32343,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="491" spans="1:14">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>2239</v>
       </c>
@@ -32383,7 +32387,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="492" spans="1:14">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>2244</v>
       </c>
@@ -32427,7 +32431,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="493" spans="1:14">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>2248</v>
       </c>
@@ -32471,7 +32475,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="494" spans="1:14">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>2251</v>
       </c>
@@ -32515,7 +32519,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="495" spans="1:14">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>2256</v>
       </c>
@@ -32559,7 +32563,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="496" spans="1:14">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>2261</v>
       </c>
@@ -32603,7 +32607,7 @@
         <v>2262</v>
       </c>
     </row>
-    <row r="497" spans="1:14">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>2263</v>
       </c>
@@ -32647,7 +32651,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="498" spans="1:14">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>2268</v>
       </c>
@@ -32691,7 +32695,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="499" spans="1:14">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>2270</v>
       </c>
@@ -32735,7 +32739,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="500" spans="1:14">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>2275</v>
       </c>
@@ -32779,7 +32783,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="501" spans="1:14">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>2279</v>
       </c>
@@ -32823,7 +32827,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="502" spans="1:14">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>2281</v>
       </c>
@@ -32867,7 +32871,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="503" spans="1:14">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>2284</v>
       </c>
@@ -32911,7 +32915,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="504" spans="1:14">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>2287</v>
       </c>
@@ -32955,7 +32959,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="505" spans="1:14">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>2289</v>
       </c>
@@ -32999,7 +33003,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="506" spans="1:14">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>2292</v>
       </c>
@@ -33043,7 +33047,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="507" spans="1:14">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>2294</v>
       </c>
@@ -33087,7 +33091,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="508" spans="1:14">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>2299</v>
       </c>
@@ -33131,7 +33135,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="509" spans="1:14">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>2304</v>
       </c>
@@ -33175,7 +33179,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="510" spans="1:14">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>2310</v>
       </c>
@@ -33219,7 +33223,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="511" spans="1:14">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>2315</v>
       </c>
@@ -33263,7 +33267,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="512" spans="1:14">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>2319</v>
       </c>
@@ -33307,7 +33311,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="513" spans="1:14">
+    <row r="513" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>2324</v>
       </c>
@@ -33351,7 +33355,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="514" spans="1:14">
+    <row r="514" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>2329</v>
       </c>
@@ -33395,7 +33399,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="515" spans="1:14">
+    <row r="515" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>2334</v>
       </c>
@@ -33439,7 +33443,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="516" spans="1:14">
+    <row r="516" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>2339</v>
       </c>
@@ -33483,7 +33487,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="517" spans="1:14">
+    <row r="517" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>2343</v>
       </c>
@@ -33527,7 +33531,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="518" spans="1:14">
+    <row r="518" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>2348</v>
       </c>
@@ -33571,7 +33575,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="519" spans="1:14">
+    <row r="519" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>2353</v>
       </c>
@@ -33615,7 +33619,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="520" spans="1:14">
+    <row r="520" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>2357</v>
       </c>
@@ -33659,7 +33663,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="521" spans="1:14">
+    <row r="521" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>2360</v>
       </c>
@@ -33703,7 +33707,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="522" spans="1:14">
+    <row r="522" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>2363</v>
       </c>
@@ -33747,7 +33751,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="523" spans="1:14">
+    <row r="523" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>2366</v>
       </c>
@@ -33791,7 +33795,7 @@
         <v>2368</v>
       </c>
     </row>
-    <row r="524" spans="1:14">
+    <row r="524" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>2369</v>
       </c>
@@ -33835,7 +33839,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="525" spans="1:14">
+    <row r="525" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>2374</v>
       </c>
@@ -33879,7 +33883,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="526" spans="1:14">
+    <row r="526" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>2379</v>
       </c>
@@ -33923,7 +33927,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="527" spans="1:14">
+    <row r="527" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>2384</v>
       </c>
@@ -33967,7 +33971,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="528" spans="1:14">
+    <row r="528" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>2389</v>
       </c>
@@ -34011,7 +34015,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="529" spans="1:14">
+    <row r="529" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>2394</v>
       </c>
@@ -34055,7 +34059,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="530" spans="1:14">
+    <row r="530" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>2399</v>
       </c>
@@ -34099,7 +34103,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="531" spans="1:14">
+    <row r="531" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>2404</v>
       </c>
@@ -34143,7 +34147,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="532" spans="1:14">
+    <row r="532" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>2409</v>
       </c>
@@ -34187,7 +34191,7 @@
         <v>2413</v>
       </c>
     </row>
-    <row r="533" spans="1:14">
+    <row r="533" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>2414</v>
       </c>
@@ -34231,7 +34235,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="534" spans="1:14">
+    <row r="534" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>2419</v>
       </c>
@@ -34275,7 +34279,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="535" spans="1:14">
+    <row r="535" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>2424</v>
       </c>
@@ -34319,7 +34323,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="536" spans="1:14">
+    <row r="536" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>2429</v>
       </c>
@@ -34363,7 +34367,7 @@
         <v>2432</v>
       </c>
     </row>
-    <row r="537" spans="1:14">
+    <row r="537" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>2433</v>
       </c>
@@ -34407,7 +34411,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="538" spans="1:14">
+    <row r="538" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>2438</v>
       </c>
@@ -34451,7 +34455,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="539" spans="1:14">
+    <row r="539" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>2441</v>
       </c>
@@ -34495,7 +34499,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="540" spans="1:14">
+    <row r="540" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>2446</v>
       </c>
@@ -34539,7 +34543,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="541" spans="1:14">
+    <row r="541" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>2451</v>
       </c>
@@ -34583,7 +34587,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="542" spans="1:14">
+    <row r="542" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>2456</v>
       </c>
@@ -34627,7 +34631,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="543" spans="1:14">
+    <row r="543" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>2461</v>
       </c>
@@ -34671,7 +34675,7 @@
         <v>2462</v>
       </c>
     </row>
-    <row r="544" spans="1:14">
+    <row r="544" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>2463</v>
       </c>
@@ -34715,7 +34719,7 @@
         <v>2467</v>
       </c>
     </row>
-    <row r="545" spans="1:14">
+    <row r="545" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>2468</v>
       </c>
@@ -34759,7 +34763,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="546" spans="1:14">
+    <row r="546" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>2473</v>
       </c>
@@ -34803,7 +34807,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="547" spans="1:14">
+    <row r="547" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>2478</v>
       </c>
@@ -34847,7 +34851,7 @@
         <v>2482</v>
       </c>
     </row>
-    <row r="548" spans="1:14">
+    <row r="548" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>2483</v>
       </c>
@@ -34891,7 +34895,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="549" spans="1:14">
+    <row r="549" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>2488</v>
       </c>
@@ -34935,7 +34939,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="550" spans="1:14">
+    <row r="550" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>2491</v>
       </c>
@@ -34979,7 +34983,7 @@
         <v>2495</v>
       </c>
     </row>
-    <row r="551" spans="1:14">
+    <row r="551" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>2496</v>
       </c>
@@ -35023,7 +35027,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="552" spans="1:14">
+    <row r="552" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>2501</v>
       </c>
@@ -35067,7 +35071,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="553" spans="1:14">
+    <row r="553" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>2506</v>
       </c>
@@ -35111,7 +35115,7 @@
         <v>2510</v>
       </c>
     </row>
-    <row r="554" spans="1:14">
+    <row r="554" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>2511</v>
       </c>
@@ -35155,7 +35159,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="555" spans="1:14">
+    <row r="555" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>2516</v>
       </c>
@@ -35199,7 +35203,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="556" spans="1:14">
+    <row r="556" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>2519</v>
       </c>
@@ -35243,7 +35247,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="557" spans="1:14">
+    <row r="557" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>2524</v>
       </c>
@@ -35287,7 +35291,7 @@
         <v>2528</v>
       </c>
     </row>
-    <row r="558" spans="1:14">
+    <row r="558" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>2529</v>
       </c>
@@ -35331,7 +35335,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="559" spans="1:14">
+    <row r="559" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>2534</v>
       </c>
@@ -35375,7 +35379,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="560" spans="1:14">
+    <row r="560" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>2540</v>
       </c>
@@ -35419,7 +35423,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="561" spans="1:14">
+    <row r="561" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>2542</v>
       </c>
@@ -35463,7 +35467,7 @@
         <v>2546</v>
       </c>
     </row>
-    <row r="562" spans="1:14">
+    <row r="562" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>2547</v>
       </c>
@@ -35507,7 +35511,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="563" spans="1:14">
+    <row r="563" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>2552</v>
       </c>
@@ -35551,7 +35555,7 @@
         <v>2556</v>
       </c>
     </row>
-    <row r="564" spans="1:14">
+    <row r="564" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>2557</v>
       </c>
@@ -35595,7 +35599,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="565" spans="1:14">
+    <row r="565" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>2562</v>
       </c>
@@ -35639,7 +35643,7 @@
         <v>2566</v>
       </c>
     </row>
-    <row r="566" spans="1:14">
+    <row r="566" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>2567</v>
       </c>
@@ -35683,7 +35687,7 @@
         <v>2571</v>
       </c>
     </row>
-    <row r="567" spans="1:14">
+    <row r="567" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>2572</v>
       </c>
@@ -35727,7 +35731,7 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="568" spans="1:14">
+    <row r="568" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>2576</v>
       </c>
@@ -35771,7 +35775,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="569" spans="1:14">
+    <row r="569" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>2580</v>
       </c>
@@ -35815,7 +35819,7 @@
         <v>2583</v>
       </c>
     </row>
-    <row r="570" spans="1:14">
+    <row r="570" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>2584</v>
       </c>
@@ -35859,7 +35863,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="571" spans="1:14">
+    <row r="571" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>2588</v>
       </c>
@@ -35903,7 +35907,7 @@
         <v>2591</v>
       </c>
     </row>
-    <row r="572" spans="1:14">
+    <row r="572" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>2592</v>
       </c>
@@ -35947,7 +35951,7 @@
         <v>2595</v>
       </c>
     </row>
-    <row r="573" spans="1:14">
+    <row r="573" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>2596</v>
       </c>
@@ -35991,7 +35995,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="574" spans="1:14">
+    <row r="574" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>2600</v>
       </c>
@@ -36035,7 +36039,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="575" spans="1:14">
+    <row r="575" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>2605</v>
       </c>
@@ -36079,7 +36083,7 @@
         <v>2609</v>
       </c>
     </row>
-    <row r="576" spans="1:14">
+    <row r="576" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>2610</v>
       </c>
@@ -36123,7 +36127,7 @@
         <v>2614</v>
       </c>
     </row>
-    <row r="577" spans="1:14">
+    <row r="577" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>2615</v>
       </c>
@@ -36167,7 +36171,7 @@
         <v>2619</v>
       </c>
     </row>
-    <row r="578" spans="1:14">
+    <row r="578" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>2620</v>
       </c>
@@ -36211,7 +36215,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="579" spans="1:14">
+    <row r="579" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>2625</v>
       </c>
@@ -36255,7 +36259,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="580" spans="1:14">
+    <row r="580" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>2628</v>
       </c>
@@ -36299,7 +36303,7 @@
         <v>2632</v>
       </c>
     </row>
-    <row r="581" spans="1:14">
+    <row r="581" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>2633</v>
       </c>
@@ -36343,7 +36347,7 @@
         <v>2637</v>
       </c>
     </row>
-    <row r="582" spans="1:14">
+    <row r="582" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>2638</v>
       </c>
@@ -36387,7 +36391,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="583" spans="1:14">
+    <row r="583" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>2640</v>
       </c>
@@ -36431,7 +36435,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="584" spans="1:14">
+    <row r="584" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>2643</v>
       </c>
@@ -36475,7 +36479,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="585" spans="1:14">
+    <row r="585" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>2645</v>
       </c>
@@ -36519,7 +36523,7 @@
         <v>2646</v>
       </c>
     </row>
-    <row r="586" spans="1:14">
+    <row r="586" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>2647</v>
       </c>
@@ -36563,7 +36567,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="587" spans="1:14">
+    <row r="587" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>2651</v>
       </c>
@@ -36607,7 +36611,7 @@
         <v>2652</v>
       </c>
     </row>
-    <row r="588" spans="1:14">
+    <row r="588" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>2653</v>
       </c>
@@ -36651,7 +36655,7 @@
         <v>2654</v>
       </c>
     </row>
-    <row r="589" spans="1:14">
+    <row r="589" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>2655</v>
       </c>
@@ -36695,7 +36699,7 @@
         <v>2657</v>
       </c>
     </row>
-    <row r="590" spans="1:14">
+    <row r="590" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>2658</v>
       </c>
@@ -36739,7 +36743,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="591" spans="1:14">
+    <row r="591" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>2660</v>
       </c>
@@ -36783,7 +36787,7 @@
         <v>2661</v>
       </c>
     </row>
-    <row r="592" spans="1:14">
+    <row r="592" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>2662</v>
       </c>
@@ -36827,7 +36831,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="593" spans="1:14">
+    <row r="593" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>2664</v>
       </c>
@@ -36871,7 +36875,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="594" spans="1:14">
+    <row r="594" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>2669</v>
       </c>
@@ -36915,7 +36919,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="595" spans="1:14">
+    <row r="595" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>2675</v>
       </c>
@@ -36959,7 +36963,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="596" spans="1:14">
+    <row r="596" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>2678</v>
       </c>
@@ -37003,7 +37007,7 @@
         <v>2682</v>
       </c>
     </row>
-    <row r="597" spans="1:14">
+    <row r="597" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>2683</v>
       </c>
@@ -37047,7 +37051,7 @@
         <v>2687</v>
       </c>
     </row>
-    <row r="598" spans="1:14">
+    <row r="598" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>2688</v>
       </c>
@@ -37091,7 +37095,7 @@
         <v>2692</v>
       </c>
     </row>
-    <row r="599" spans="1:14">
+    <row r="599" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>2693</v>
       </c>
@@ -37135,7 +37139,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="600" spans="1:14">
+    <row r="600" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>2698</v>
       </c>
@@ -37179,7 +37183,7 @@
         <v>2702</v>
       </c>
     </row>
-    <row r="601" spans="1:14">
+    <row r="601" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>2703</v>
       </c>
@@ -37223,7 +37227,7 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="602" spans="1:14">
+    <row r="602" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>2708</v>
       </c>
@@ -37267,7 +37271,7 @@
         <v>2711</v>
       </c>
     </row>
-    <row r="603" spans="1:14">
+    <row r="603" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>2712</v>
       </c>
@@ -37311,7 +37315,7 @@
         <v>2717</v>
       </c>
     </row>
-    <row r="604" spans="1:14">
+    <row r="604" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>2718</v>
       </c>
@@ -37355,7 +37359,7 @@
         <v>2722</v>
       </c>
     </row>
-    <row r="605" spans="1:14">
+    <row r="605" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>2723</v>
       </c>
@@ -37399,7 +37403,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="606" spans="1:14">
+    <row r="606" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>2728</v>
       </c>
@@ -37443,7 +37447,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="607" spans="1:14">
+    <row r="607" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>2732</v>
       </c>
@@ -37487,7 +37491,7 @@
         <v>2736</v>
       </c>
     </row>
-    <row r="608" spans="1:14">
+    <row r="608" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>2737</v>
       </c>
@@ -37531,7 +37535,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="609" spans="1:14">
+    <row r="609" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>2742</v>
       </c>
@@ -37575,7 +37579,7 @@
         <v>2744</v>
       </c>
     </row>
-    <row r="610" spans="1:14">
+    <row r="610" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>2745</v>
       </c>
@@ -37619,7 +37623,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="611" spans="1:14">
+    <row r="611" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>2747</v>
       </c>
@@ -37663,7 +37667,7 @@
         <v>2748</v>
       </c>
     </row>
-    <row r="612" spans="1:14">
+    <row r="612" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>2749</v>
       </c>
@@ -37707,7 +37711,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="613" spans="1:14">
+    <row r="613" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>2751</v>
       </c>
@@ -37751,7 +37755,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="614" spans="1:14">
+    <row r="614" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>2754</v>
       </c>
@@ -37795,7 +37799,7 @@
         <v>2755</v>
       </c>
     </row>
-    <row r="615" spans="1:14">
+    <row r="615" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>2756</v>
       </c>
@@ -37839,7 +37843,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="616" spans="1:14">
+    <row r="616" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>2758</v>
       </c>
@@ -37883,7 +37887,7 @@
         <v>2759</v>
       </c>
     </row>
-    <row r="617" spans="1:14">
+    <row r="617" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>2760</v>
       </c>
@@ -37927,7 +37931,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="618" spans="1:14">
+    <row r="618" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>2762</v>
       </c>
@@ -37971,7 +37975,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="619" spans="1:14">
+    <row r="619" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>2767</v>
       </c>
@@ -38015,7 +38019,7 @@
         <v>2771</v>
       </c>
     </row>
-    <row r="620" spans="1:14">
+    <row r="620" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>2772</v>
       </c>
@@ -38059,7 +38063,7 @@
         <v>2777</v>
       </c>
     </row>
-    <row r="621" spans="1:14">
+    <row r="621" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>2778</v>
       </c>
@@ -38103,7 +38107,7 @@
         <v>2782</v>
       </c>
     </row>
-    <row r="622" spans="1:14">
+    <row r="622" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>2783</v>
       </c>
@@ -38147,7 +38151,7 @@
         <v>2787</v>
       </c>
     </row>
-    <row r="623" spans="1:14">
+    <row r="623" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>2788</v>
       </c>
@@ -38191,7 +38195,7 @@
         <v>2792</v>
       </c>
     </row>
-    <row r="624" spans="1:14">
+    <row r="624" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>2793</v>
       </c>
@@ -38235,7 +38239,7 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="625" spans="1:14">
+    <row r="625" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>2798</v>
       </c>
@@ -38279,7 +38283,7 @@
         <v>2803</v>
       </c>
     </row>
-    <row r="626" spans="1:14">
+    <row r="626" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>2804</v>
       </c>
@@ -38323,7 +38327,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="627" spans="1:14">
+    <row r="627" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>2809</v>
       </c>
@@ -38367,7 +38371,7 @@
         <v>2813</v>
       </c>
     </row>
-    <row r="628" spans="1:14">
+    <row r="628" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>2814</v>
       </c>
@@ -38411,7 +38415,7 @@
         <v>2818</v>
       </c>
     </row>
-    <row r="629" spans="1:14">
+    <row r="629" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>2819</v>
       </c>
@@ -38455,7 +38459,7 @@
         <v>2823</v>
       </c>
     </row>
-    <row r="630" spans="1:14">
+    <row r="630" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>2824</v>
       </c>
@@ -38499,7 +38503,7 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="631" spans="1:14">
+    <row r="631" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>2829</v>
       </c>
@@ -38543,7 +38547,7 @@
         <v>2833</v>
       </c>
     </row>
-    <row r="632" spans="1:14">
+    <row r="632" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>2834</v>
       </c>
@@ -38587,7 +38591,7 @@
         <v>2836</v>
       </c>
     </row>
-    <row r="633" spans="1:14">
+    <row r="633" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>2837</v>
       </c>
@@ -38631,7 +38635,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="634" spans="1:14">
+    <row r="634" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>2841</v>
       </c>
@@ -38675,7 +38679,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="635" spans="1:14">
+    <row r="635" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>2843</v>
       </c>
@@ -38719,7 +38723,7 @@
         <v>2844</v>
       </c>
     </row>
-    <row r="636" spans="1:14">
+    <row r="636" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>2845</v>
       </c>
@@ -38763,7 +38767,7 @@
         <v>2849</v>
       </c>
     </row>
-    <row r="637" spans="1:14">
+    <row r="637" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>2850</v>
       </c>
@@ -38807,7 +38811,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="638" spans="1:14">
+    <row r="638" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>2855</v>
       </c>
@@ -38851,7 +38855,7 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="639" spans="1:14">
+    <row r="639" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>2860</v>
       </c>
@@ -38895,7 +38899,7 @@
         <v>2865</v>
       </c>
     </row>
-    <row r="640" spans="1:14">
+    <row r="640" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>2866</v>
       </c>
@@ -38939,7 +38943,7 @@
         <v>2870</v>
       </c>
     </row>
-    <row r="641" spans="1:14">
+    <row r="641" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>2871</v>
       </c>
@@ -38983,7 +38987,7 @@
         <v>2875</v>
       </c>
     </row>
-    <row r="642" spans="1:14">
+    <row r="642" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>2876</v>
       </c>
@@ -39027,7 +39031,7 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="643" spans="1:14">
+    <row r="643" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>2881</v>
       </c>
@@ -39071,7 +39075,7 @@
         <v>2884</v>
       </c>
     </row>
-    <row r="644" spans="1:14">
+    <row r="644" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>2885</v>
       </c>
@@ -39115,7 +39119,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="645" spans="1:14">
+    <row r="645" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>2889</v>
       </c>
@@ -39159,7 +39163,7 @@
         <v>2893</v>
       </c>
     </row>
-    <row r="646" spans="1:14">
+    <row r="646" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>2894</v>
       </c>
@@ -39203,7 +39207,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="647" spans="1:14">
+    <row r="647" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>2900</v>
       </c>
@@ -39247,7 +39251,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="648" spans="1:14">
+    <row r="648" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>2905</v>
       </c>
@@ -39291,7 +39295,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="649" spans="1:14">
+    <row r="649" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>2907</v>
       </c>
@@ -39335,7 +39339,7 @@
         <v>2908</v>
       </c>
     </row>
-    <row r="650" spans="1:14">
+    <row r="650" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>2909</v>
       </c>
@@ -39379,7 +39383,7 @@
         <v>2910</v>
       </c>
     </row>
-    <row r="651" spans="1:14">
+    <row r="651" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>2911</v>
       </c>
@@ -39423,7 +39427,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="652" spans="1:14">
+    <row r="652" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>2914</v>
       </c>
@@ -39467,7 +39471,7 @@
         <v>2918</v>
       </c>
     </row>
-    <row r="653" spans="1:14">
+    <row r="653" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>2919</v>
       </c>
@@ -39511,7 +39515,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="654" spans="1:14">
+    <row r="654" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>2924</v>
       </c>
@@ -39555,7 +39559,7 @@
         <v>2927</v>
       </c>
     </row>
-    <row r="655" spans="1:14">
+    <row r="655" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>2928</v>
       </c>
@@ -39599,7 +39603,7 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="656" spans="1:14">
+    <row r="656" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>2930</v>
       </c>
@@ -39643,7 +39647,7 @@
         <v>2933</v>
       </c>
     </row>
-    <row r="657" spans="1:14">
+    <row r="657" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>2934</v>
       </c>
@@ -39687,7 +39691,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="658" spans="1:14">
+    <row r="658" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>2936</v>
       </c>
@@ -39731,7 +39735,7 @@
         <v>2939</v>
       </c>
     </row>
-    <row r="659" spans="1:14">
+    <row r="659" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>2940</v>
       </c>
@@ -39775,7 +39779,7 @@
         <v>2944</v>
       </c>
     </row>
-    <row r="660" spans="1:14">
+    <row r="660" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>2945</v>
       </c>
@@ -39819,7 +39823,7 @@
         <v>2948</v>
       </c>
     </row>
-    <row r="661" spans="1:14">
+    <row r="661" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>2949</v>
       </c>
@@ -39863,7 +39867,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="662" spans="1:14">
+    <row r="662" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>2955</v>
       </c>
@@ -39907,7 +39911,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="663" spans="1:14">
+    <row r="663" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>2961</v>
       </c>
@@ -39951,7 +39955,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="664" spans="1:14">
+    <row r="664" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>2965</v>
       </c>
@@ -39995,7 +39999,7 @@
         <v>2966</v>
       </c>
     </row>
-    <row r="665" spans="1:14">
+    <row r="665" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>2967</v>
       </c>
@@ -40039,7 +40043,7 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="666" spans="1:14">
+    <row r="666" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>2971</v>
       </c>
@@ -40083,7 +40087,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="667" spans="1:14">
+    <row r="667" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>2976</v>
       </c>
@@ -40127,7 +40131,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="668" spans="1:14">
+    <row r="668" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>2979</v>
       </c>
@@ -40171,7 +40175,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="669" spans="1:14">
+    <row r="669" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>2985</v>
       </c>
@@ -40215,7 +40219,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="670" spans="1:14">
+    <row r="670" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>2991</v>
       </c>
@@ -40259,7 +40263,7 @@
         <v>2995</v>
       </c>
     </row>
-    <row r="671" spans="1:14">
+    <row r="671" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>2996</v>
       </c>
@@ -40303,7 +40307,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="672" spans="1:14">
+    <row r="672" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>3001</v>
       </c>
@@ -40347,7 +40351,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="673" spans="1:14">
+    <row r="673" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>3007</v>
       </c>
@@ -40391,7 +40395,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="674" spans="1:14">
+    <row r="674" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>3013</v>
       </c>
@@ -40435,7 +40439,7 @@
         <v>3017</v>
       </c>
     </row>
-    <row r="675" spans="1:14">
+    <row r="675" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>3018</v>
       </c>
@@ -40479,7 +40483,7 @@
         <v>3022</v>
       </c>
     </row>
-    <row r="676" spans="1:14">
+    <row r="676" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>3023</v>
       </c>
@@ -40523,7 +40527,7 @@
         <v>3027</v>
       </c>
     </row>
-    <row r="677" spans="1:14">
+    <row r="677" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>3028</v>
       </c>
@@ -40567,7 +40571,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="678" spans="1:14">
+    <row r="678" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>3032</v>
       </c>
@@ -40611,7 +40615,7 @@
         <v>3036</v>
       </c>
     </row>
-    <row r="679" spans="1:14">
+    <row r="679" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>3037</v>
       </c>
@@ -40655,7 +40659,7 @@
         <v>3041</v>
       </c>
     </row>
-    <row r="680" spans="1:14">
+    <row r="680" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>3042</v>
       </c>
@@ -40699,7 +40703,7 @@
         <v>3047</v>
       </c>
     </row>
-    <row r="681" spans="1:14">
+    <row r="681" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>3048</v>
       </c>
@@ -40743,7 +40747,7 @@
         <v>3052</v>
       </c>
     </row>
-    <row r="682" spans="1:14">
+    <row r="682" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>3053</v>
       </c>
@@ -40787,7 +40791,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="683" spans="1:14">
+    <row r="683" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>3055</v>
       </c>
@@ -40831,7 +40835,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="684" spans="1:14">
+    <row r="684" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>3057</v>
       </c>
@@ -40875,7 +40879,7 @@
         <v>3062</v>
       </c>
     </row>
-    <row r="685" spans="1:14">
+    <row r="685" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>3063</v>
       </c>
@@ -40919,7 +40923,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="686" spans="1:14">
+    <row r="686" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>3069</v>
       </c>
@@ -40963,7 +40967,7 @@
         <v>3070</v>
       </c>
     </row>
-    <row r="687" spans="1:14">
+    <row r="687" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>3071</v>
       </c>
@@ -41007,7 +41011,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="688" spans="1:14">
+    <row r="688" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>3075</v>
       </c>
@@ -41051,7 +41055,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="689" spans="1:14">
+    <row r="689" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>3079</v>
       </c>
@@ -41095,7 +41099,7 @@
         <v>3083</v>
       </c>
     </row>
-    <row r="690" spans="1:14">
+    <row r="690" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>3084</v>
       </c>
@@ -41139,7 +41143,7 @@
         <v>3088</v>
       </c>
     </row>
-    <row r="691" spans="1:14">
+    <row r="691" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>3089</v>
       </c>
@@ -41183,7 +41187,7 @@
         <v>3094</v>
       </c>
     </row>
-    <row r="692" spans="1:14">
+    <row r="692" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>3095</v>
       </c>
@@ -41227,7 +41231,7 @@
         <v>3099</v>
       </c>
     </row>
-    <row r="693" spans="1:14">
+    <row r="693" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>3100</v>
       </c>
@@ -41271,7 +41275,7 @@
         <v>3104</v>
       </c>
     </row>
-    <row r="694" spans="1:14">
+    <row r="694" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>3105</v>
       </c>
@@ -41315,7 +41319,7 @@
         <v>3109</v>
       </c>
     </row>
-    <row r="695" spans="1:14">
+    <row r="695" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>3110</v>
       </c>
@@ -41359,7 +41363,7 @@
         <v>3115</v>
       </c>
     </row>
-    <row r="696" spans="1:14">
+    <row r="696" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>3116</v>
       </c>
@@ -41403,7 +41407,7 @@
         <v>3119</v>
       </c>
     </row>
-    <row r="697" spans="1:14">
+    <row r="697" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>3120</v>
       </c>
@@ -41447,7 +41451,7 @@
         <v>3124</v>
       </c>
     </row>
-    <row r="698" spans="1:14">
+    <row r="698" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>3125</v>
       </c>
@@ -41491,7 +41495,7 @@
         <v>3130</v>
       </c>
     </row>
-    <row r="699" spans="1:14">
+    <row r="699" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>3131</v>
       </c>
@@ -41535,7 +41539,7 @@
         <v>3136</v>
       </c>
     </row>
-    <row r="700" spans="1:14">
+    <row r="700" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>3137</v>
       </c>
@@ -41579,7 +41583,7 @@
         <v>3141</v>
       </c>
     </row>
-    <row r="701" spans="1:14">
+    <row r="701" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>3142</v>
       </c>
@@ -41623,7 +41627,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="702" spans="1:14">
+    <row r="702" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>3146</v>
       </c>
@@ -41667,7 +41671,7 @@
         <v>3151</v>
       </c>
     </row>
-    <row r="703" spans="1:14">
+    <row r="703" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>3152</v>
       </c>
@@ -41711,7 +41715,7 @@
         <v>3153</v>
       </c>
     </row>
-    <row r="704" spans="1:14">
+    <row r="704" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>3154</v>
       </c>
@@ -41755,7 +41759,7 @@
         <v>3157</v>
       </c>
     </row>
-    <row r="705" spans="1:14">
+    <row r="705" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>3158</v>
       </c>
@@ -41799,7 +41803,7 @@
         <v>3162</v>
       </c>
     </row>
-    <row r="706" spans="1:14">
+    <row r="706" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>3163</v>
       </c>
@@ -41843,7 +41847,7 @@
         <v>3167</v>
       </c>
     </row>
-    <row r="707" spans="1:14">
+    <row r="707" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>3168</v>
       </c>
@@ -41887,7 +41891,7 @@
         <v>3172</v>
       </c>
     </row>
-    <row r="708" spans="1:14">
+    <row r="708" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>3173</v>
       </c>
@@ -41931,7 +41935,7 @@
         <v>3177</v>
       </c>
     </row>
-    <row r="709" spans="1:14">
+    <row r="709" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>3178</v>
       </c>
@@ -41975,7 +41979,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="710" spans="1:14">
+    <row r="710" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>3183</v>
       </c>
@@ -42019,7 +42023,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="711" spans="1:14">
+    <row r="711" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>3186</v>
       </c>
@@ -42063,7 +42067,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="712" spans="1:14">
+    <row r="712" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>3191</v>
       </c>
@@ -42107,7 +42111,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="713" spans="1:14">
+    <row r="713" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>3196</v>
       </c>
@@ -42151,7 +42155,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="714" spans="1:14">
+    <row r="714" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>3201</v>
       </c>
@@ -42195,7 +42199,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="715" spans="1:14">
+    <row r="715" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>3206</v>
       </c>
@@ -42239,7 +42243,7 @@
         <v>3210</v>
       </c>
     </row>
-    <row r="716" spans="1:14">
+    <row r="716" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>3211</v>
       </c>
@@ -42283,7 +42287,7 @@
         <v>3213</v>
       </c>
     </row>
-    <row r="717" spans="1:14">
+    <row r="717" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>3214</v>
       </c>
@@ -42327,7 +42331,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="718" spans="1:14">
+    <row r="718" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>3216</v>
       </c>
@@ -42371,7 +42375,7 @@
         <v>3218</v>
       </c>
     </row>
-    <row r="719" spans="1:14">
+    <row r="719" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>3219</v>
       </c>
@@ -42415,7 +42419,7 @@
         <v>3223</v>
       </c>
     </row>
-    <row r="720" spans="1:14">
+    <row r="720" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>3224</v>
       </c>
@@ -42459,7 +42463,7 @@
         <v>3228</v>
       </c>
     </row>
-    <row r="721" spans="1:14">
+    <row r="721" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>3229</v>
       </c>
@@ -42503,7 +42507,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="722" spans="1:14">
+    <row r="722" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>3234</v>
       </c>
@@ -42547,7 +42551,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="723" spans="1:14">
+    <row r="723" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>3239</v>
       </c>
@@ -42591,7 +42595,7 @@
         <v>3243</v>
       </c>
     </row>
-    <row r="724" spans="1:14">
+    <row r="724" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>3244</v>
       </c>
@@ -42635,7 +42639,7 @@
         <v>3248</v>
       </c>
     </row>
-    <row r="725" spans="1:14">
+    <row r="725" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>3249</v>
       </c>
@@ -42679,7 +42683,7 @@
         <v>3253</v>
       </c>
     </row>
-    <row r="726" spans="1:14">
+    <row r="726" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>3254</v>
       </c>
@@ -42723,7 +42727,7 @@
         <v>3258</v>
       </c>
     </row>
-    <row r="727" spans="1:14">
+    <row r="727" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>3259</v>
       </c>
@@ -42767,7 +42771,7 @@
         <v>3263</v>
       </c>
     </row>
-    <row r="728" spans="1:14">
+    <row r="728" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>3264</v>
       </c>
@@ -42811,7 +42815,7 @@
         <v>3268</v>
       </c>
     </row>
-    <row r="729" spans="1:14">
+    <row r="729" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>3269</v>
       </c>
@@ -42855,7 +42859,7 @@
         <v>3274</v>
       </c>
     </row>
-    <row r="730" spans="1:14">
+    <row r="730" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>3275</v>
       </c>
@@ -42899,7 +42903,7 @@
         <v>3279</v>
       </c>
     </row>
-    <row r="731" spans="1:14">
+    <row r="731" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>3280</v>
       </c>
@@ -42943,7 +42947,7 @@
         <v>3284</v>
       </c>
     </row>
-    <row r="732" spans="1:14">
+    <row r="732" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>3285</v>
       </c>
@@ -42987,7 +42991,7 @@
         <v>3289</v>
       </c>
     </row>
-    <row r="733" spans="1:14">
+    <row r="733" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>3290</v>
       </c>
@@ -43031,7 +43035,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="734" spans="1:14">
+    <row r="734" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>3295</v>
       </c>
@@ -43075,7 +43079,7 @@
         <v>3299</v>
       </c>
     </row>
-    <row r="735" spans="1:14">
+    <row r="735" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>3300</v>
       </c>
@@ -43119,7 +43123,7 @@
         <v>3304</v>
       </c>
     </row>
-    <row r="736" spans="1:14">
+    <row r="736" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>3305</v>
       </c>
@@ -43163,7 +43167,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="737" spans="1:14">
+    <row r="737" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>3310</v>
       </c>
@@ -43207,7 +43211,7 @@
         <v>3314</v>
       </c>
     </row>
-    <row r="738" spans="1:14">
+    <row r="738" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>3315</v>
       </c>
@@ -43251,7 +43255,7 @@
         <v>3319</v>
       </c>
     </row>
-    <row r="739" spans="1:14">
+    <row r="739" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>3320</v>
       </c>
@@ -43295,7 +43299,7 @@
         <v>3324</v>
       </c>
     </row>
-    <row r="740" spans="1:14">
+    <row r="740" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>3325</v>
       </c>
@@ -43339,7 +43343,7 @@
         <v>3329</v>
       </c>
     </row>
-    <row r="741" spans="1:14">
+    <row r="741" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>3330</v>
       </c>
@@ -43383,7 +43387,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="742" spans="1:14">
+    <row r="742" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>3335</v>
       </c>
@@ -43427,7 +43431,7 @@
         <v>3339</v>
       </c>
     </row>
-    <row r="743" spans="1:14">
+    <row r="743" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>3340</v>
       </c>
@@ -43471,7 +43475,7 @@
         <v>3344</v>
       </c>
     </row>
-    <row r="744" spans="1:14">
+    <row r="744" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>3345</v>
       </c>
@@ -43515,7 +43519,7 @@
         <v>3349</v>
       </c>
     </row>
-    <row r="745" spans="1:14">
+    <row r="745" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>3350</v>
       </c>
@@ -43559,7 +43563,7 @@
         <v>3354</v>
       </c>
     </row>
-    <row r="746" spans="1:14">
+    <row r="746" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>3355</v>
       </c>
@@ -43603,7 +43607,7 @@
         <v>3358</v>
       </c>
     </row>
-    <row r="747" spans="1:14">
+    <row r="747" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>3359</v>
       </c>
@@ -43647,7 +43651,7 @@
         <v>3362</v>
       </c>
     </row>
-    <row r="748" spans="1:14">
+    <row r="748" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>3363</v>
       </c>
@@ -43691,7 +43695,7 @@
         <v>3367</v>
       </c>
     </row>
-    <row r="749" spans="1:14">
+    <row r="749" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>3368</v>
       </c>
@@ -43735,7 +43739,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="750" spans="1:14">
+    <row r="750" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>3373</v>
       </c>
@@ -43779,7 +43783,7 @@
         <v>3377</v>
       </c>
     </row>
-    <row r="751" spans="1:14">
+    <row r="751" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>3378</v>
       </c>
@@ -43823,7 +43827,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="752" spans="1:14">
+    <row r="752" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>3383</v>
       </c>
@@ -43867,7 +43871,7 @@
         <v>3387</v>
       </c>
     </row>
-    <row r="753" spans="1:14">
+    <row r="753" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>3388</v>
       </c>
@@ -43911,7 +43915,7 @@
         <v>3392</v>
       </c>
     </row>
-    <row r="754" spans="1:14">
+    <row r="754" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>3393</v>
       </c>
@@ -43955,7 +43959,7 @@
         <v>3397</v>
       </c>
     </row>
-    <row r="755" spans="1:14">
+    <row r="755" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>3398</v>
       </c>
@@ -43999,7 +44003,7 @@
         <v>3401</v>
       </c>
     </row>
-    <row r="756" spans="1:14">
+    <row r="756" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>3402</v>
       </c>
@@ -44043,7 +44047,7 @@
         <v>3405</v>
       </c>
     </row>
-    <row r="757" spans="1:14">
+    <row r="757" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>3406</v>
       </c>
@@ -44087,7 +44091,7 @@
         <v>3409</v>
       </c>
     </row>
-    <row r="758" spans="1:14">
+    <row r="758" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>3410</v>
       </c>
@@ -44131,7 +44135,7 @@
         <v>3413</v>
       </c>
     </row>
-    <row r="759" spans="1:14">
+    <row r="759" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>3414</v>
       </c>
@@ -44175,7 +44179,7 @@
         <v>3418</v>
       </c>
     </row>
-    <row r="760" spans="1:14">
+    <row r="760" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>3419</v>
       </c>
@@ -44219,7 +44223,7 @@
         <v>3422</v>
       </c>
     </row>
-    <row r="761" spans="1:14">
+    <row r="761" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>3423</v>
       </c>
@@ -44263,7 +44267,7 @@
         <v>3426</v>
       </c>
     </row>
-    <row r="762" spans="1:14">
+    <row r="762" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>3427</v>
       </c>
@@ -44307,7 +44311,7 @@
         <v>3431</v>
       </c>
     </row>
-    <row r="763" spans="1:14">
+    <row r="763" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>3432</v>
       </c>
@@ -44351,7 +44355,7 @@
         <v>3436</v>
       </c>
     </row>
-    <row r="764" spans="1:14">
+    <row r="764" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>3437</v>
       </c>
@@ -44395,7 +44399,7 @@
         <v>3440</v>
       </c>
     </row>
-    <row r="765" spans="1:14">
+    <row r="765" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>3441</v>
       </c>
@@ -44439,7 +44443,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="766" spans="1:14">
+    <row r="766" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>3446</v>
       </c>
@@ -44483,7 +44487,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="767" spans="1:14">
+    <row r="767" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>3451</v>
       </c>
@@ -44527,7 +44531,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="768" spans="1:14">
+    <row r="768" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>3456</v>
       </c>

--- a/backend/data/medical_master.xlsx
+++ b/backend/data/medical_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aaba9b7fc384692a/Desktop/Ai_medical_assitant/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{7313785C-7652-4BB8-BD78-FC04FC8A3E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05705764-9340-45AC-A0C4-59BF17ECD085}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{7313785C-7652-4BB8-BD78-FC04FC8A3E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58FEEBCA-3AE0-4015-BBFE-B21B2E4047B6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0E185D9D-9B36-489F-B026-23D5259A59E6}"/>
   </bookViews>
@@ -10432,12 +10432,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -10452,8 +10458,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11629,7 +11636,7 @@
       <c r="C20" t="s">
         <v>107</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>108</v>
       </c>
       <c r="E20" t="s">
